--- a/docs/files/REPORT_FILTRI/Agente Nadir Abdel - CR BRAVI MATTEO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Nadir Abdel - CR BRAVI MATTEO.xlsx
@@ -684,13 +684,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1102</v>
+        <v>1091</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>833</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>960</v>
+        <v>941</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>705</v>
+        <v>688</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>672</v>
+        <v>657</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1280</v>
+        <v>1256</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>258</v>
@@ -863,10 +863,10 @@
         <v>180</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>1030</v>
+        <v>1009</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>120</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>90</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>52</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>15</v>
@@ -972,7 +972,7 @@
         <v>24</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>25</v>
@@ -981,10 +981,10 @@
         <v>16</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>110</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>15</v>
@@ -1081,7 +1081,7 @@
         <v>69</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>25</v>
@@ -1090,7 +1090,7 @@
         <v>103</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>14</v>
